--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3933351C-987C-4691-A72C-F1D9740903FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C2FC6D-9B6E-4997-8BE7-B6AA8CC0A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>MCA (P1D2635)</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
@@ -1034,25 +1037,47 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="8">
+        <v>46250</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>120</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>45</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>455</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C2FC6D-9B6E-4997-8BE7-B6AA8CC0A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{00C2FC6D-9B6E-4997-8BE7-B6AA8CC0A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7308688-8DBD-4FDD-BD18-0BA2A00ECF45}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1081,29 +1084,53 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>120</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>55</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>400</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>265</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
+      <c r="A9" s="8">
+        <v>46252</v>
+      </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1125,7 +1152,9 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
+      <c r="A10" s="8">
+        <v>46253</v>
+      </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -1147,7 +1176,9 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
+      <c r="A11" s="8">
+        <v>46254</v>
+      </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -1169,7 +1200,9 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="8">
+        <v>46255</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{00C2FC6D-9B6E-4997-8BE7-B6AA8CC0A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7308688-8DBD-4FDD-BD18-0BA2A00ECF45}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{00C2FC6D-9B6E-4997-8BE7-B6AA8CC0A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B25E2E8-97B8-4A24-A140-DB0409EAF98D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,18 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Was Sleepy because of yesterday</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Was with my Friends</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1236,9 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
+      <c r="A13" s="8">
+        <v>46256</v>
+      </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1246,51 +1260,101 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>30</v>
+      </c>
+      <c r="E14" s="14">
+        <v>16</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>480</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1026</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>414</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>120</v>
+      </c>
+      <c r="D15" s="14">
+        <v>40</v>
+      </c>
+      <c r="E15" s="14">
+        <v>40</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>200</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="8">
+        <v>46259</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{00C2FC6D-9B6E-4997-8BE7-B6AA8CC0A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B25E2E8-97B8-4A24-A140-DB0409EAF98D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B51ED7-F446-45E9-8507-A2E41D61E73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,15 @@
   </si>
   <si>
     <t>Was with my Friends</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Very Hectic</t>
   </si>
 </sst>
 </file>
@@ -1143,120 +1152,222 @@
       <c r="A9" s="8">
         <v>46252</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="B9" s="14">
+        <v>360</v>
+      </c>
+      <c r="C9" s="14">
+        <v>100</v>
+      </c>
+      <c r="D9" s="14">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>50</v>
+      </c>
+      <c r="F9" s="14">
+        <v>400</v>
+      </c>
+      <c r="G9" s="14">
+        <v>8</v>
+      </c>
+      <c r="H9" s="14">
+        <v>100</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>46253</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>120</v>
+      </c>
+      <c r="D10" s="14">
+        <v>30</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>200</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>286</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1086</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>354</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>46254</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="B11" s="14">
+        <v>451</v>
+      </c>
+      <c r="C11" s="14">
+        <v>90</v>
+      </c>
+      <c r="D11" s="14">
+        <v>45</v>
+      </c>
+      <c r="E11" s="14">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>300</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1226</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>214</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>46255</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="B12" s="14">
+        <v>340</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>25</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>300</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>355</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>46256</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="B13" s="14">
+        <v>500</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>70</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>500</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B51ED7-F446-45E9-8507-A2E41D61E73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B6096-BAD1-4225-AFCD-71B1805DCDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B6096-BAD1-4225-AFCD-71B1805DCDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,15 @@
   </si>
   <si>
     <t>Very Hectic</t>
+  </si>
+  <si>
+    <t>Went to relative's Home.</t>
+  </si>
+  <si>
+    <t>Was feeling Tired.</t>
+  </si>
+  <si>
+    <t>Was unable to sleep</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1111,9 @@
       <c r="M7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
@@ -1146,7 +1157,9 @@
       <c r="M8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
@@ -1190,7 +1203,9 @@
       <c r="M9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="17"/>
+      <c r="N9" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7E128A3-075C-43D0-8769-CA2170B3EED6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Was unable to sleep</t>
+  </si>
+  <si>
+    <t>An Average Day</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1252,9 @@
       <c r="M10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="17"/>
+      <c r="N10" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7E128A3-075C-43D0-8769-CA2170B3EED6}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F53309A-B6D7-49CE-AD6E-770C42D3EFC2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>An Average Day</t>
+  </si>
+  <si>
+    <t>It was good</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1347,9 @@
       <c r="M12" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="N12" s="17"/>
+      <c r="N12" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
@@ -1388,7 +1393,9 @@
       <c r="M13" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F53309A-B6D7-49CE-AD6E-770C42D3EFC2}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DC8CB57-08F2-4F57-AA78-5FD58E66C2DD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>It was good</t>
+  </si>
+  <si>
+    <t>Was tired due to Heatwaves.</t>
   </si>
 </sst>
 </file>
@@ -1493,28 +1496,52 @@
       <c r="A16" s="8">
         <v>46259</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="B16" s="14">
+        <v>430</v>
+      </c>
+      <c r="C16" s="14">
+        <v>105</v>
+      </c>
+      <c r="D16" s="14">
+        <v>30</v>
+      </c>
+      <c r="E16" s="14">
+        <v>15</v>
+      </c>
+      <c r="F16" s="14">
+        <v>350</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="14">
+        <v>305</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>205</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="8">
+        <v>46260</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -1536,7 +1563,9 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="8">
+        <v>46261</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -1558,7 +1587,9 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="8">
+        <v>46262</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -1580,7 +1611,9 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="8">
+        <v>46263</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -1602,7 +1635,9 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+      <c r="A21" s="8">
+        <v>46264</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -1624,7 +1659,9 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="8">
+        <v>46265</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -1646,7 +1683,9 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="8">
+        <v>46266</v>
+      </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
@@ -1668,7 +1707,9 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="8">
+        <v>46267</v>
+      </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -1690,7 +1731,9 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
+      <c r="A25" s="8">
+        <v>46268</v>
+      </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -1712,7 +1755,9 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
+      <c r="A26" s="8">
+        <v>46269</v>
+      </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -1734,7 +1779,9 @@
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
+      <c r="A27" s="8">
+        <v>46270</v>
+      </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -1756,7 +1803,9 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
+      <c r="A28" s="8">
+        <v>46271</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -1778,7 +1827,9 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
+      <c r="A29" s="8">
+        <v>46272</v>
+      </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -1800,7 +1851,9 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
+      <c r="A30" s="8">
+        <v>46273</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -1822,7 +1875,9 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
+      <c r="A31" s="8">
+        <v>46274</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DC8CB57-08F2-4F57-AA78-5FD58E66C2DD}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92586E20-3ECB-48BC-BB85-E8A57EF53161}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1542,25 +1542,47 @@
       <c r="A17" s="8">
         <v>46260</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="B17" s="14">
+        <v>450</v>
+      </c>
+      <c r="C17" s="14">
+        <v>120</v>
+      </c>
+      <c r="D17" s="14">
+        <v>45</v>
+      </c>
+      <c r="E17" s="14">
+        <v>15</v>
+      </c>
+      <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>400</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92586E20-3ECB-48BC-BB85-E8A57EF53161}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68CE2EA5-9B2A-4C7E-BA8F-A1667FAB0FB5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>Was tired due to Heatwaves.</t>
+  </si>
+  <si>
+    <t>Was feeling tired because of yesterday's Festival.</t>
+  </si>
+  <si>
+    <t>It was Rakhi Today</t>
+  </si>
+  <si>
+    <t>Took me a lot of time buying Gifts for tomorrow</t>
   </si>
 </sst>
 </file>
@@ -1584,77 +1593,143 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>46261</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>120</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>25</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>180</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>46262</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="B19" s="14">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>50</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>50</v>
+      </c>
+      <c r="G19" s="14">
+        <v>1</v>
+      </c>
+      <c r="H19" s="14">
+        <v>600</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>46263</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="B20" s="14">
+        <v>600</v>
+      </c>
+      <c r="C20" s="14">
+        <v>120</v>
+      </c>
+      <c r="D20" s="14">
+        <v>30</v>
+      </c>
+      <c r="E20" s="14">
+        <v>10</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>400</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{12560BCD-9601-4566-84A6-BD3753E011B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68CE2EA5-9B2A-4C7E-BA8F-A1667FAB0FB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62658449-9196-4226-8434-379EFC6760C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1735,25 +1735,47 @@
       <c r="A21" s="8">
         <v>46264</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>60</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>600</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62658449-9196-4226-8434-379EFC6760C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{62658449-9196-4226-8434-379EFC6760C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC4D3A1-0980-4801-9404-081DB047DAF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Took me a lot of time buying Gifts for tomorrow</t>
+  </si>
+  <si>
+    <t>It was hectic Day</t>
   </si>
 </sst>
 </file>
@@ -1781,25 +1784,47 @@
       <c r="A22" s="8">
         <v>46265</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>120</v>
+      </c>
+      <c r="D22" s="14">
+        <v>45</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>415</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{62658449-9196-4226-8434-379EFC6760C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC4D3A1-0980-4801-9404-081DB047DAF1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492AE04F-274D-4D30-8F4C-63323E490B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,6 +267,12 @@
   <si>
     <t>It was hectic Day</t>
   </si>
+  <si>
+    <t>Was not well</t>
+  </si>
+  <si>
+    <t>It was a good Day</t>
+  </si>
 </sst>
 </file>
 
@@ -452,7 +458,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1785,33 +1803,33 @@
         <v>46265</v>
       </c>
       <c r="B22" s="14">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="C22" s="14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D22" s="14">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E22" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1025</v>
+        <v>660</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>415</v>
+        <v>780</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>58</v>
@@ -1823,56 +1841,100 @@
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>46266</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>120</v>
+      </c>
+      <c r="D23" s="14">
+        <v>45</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" ref="I23" si="2">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <v>1025</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" ref="J23" si="3">IF(I23="","",1440-I23)</f>
+        <v>415</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>46267</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="B24" s="14">
+        <v>380</v>
+      </c>
+      <c r="C24" s="14">
+        <v>105</v>
+      </c>
+      <c r="D24" s="14">
+        <v>30</v>
+      </c>
+      <c r="E24" s="14">
+        <v>25</v>
+      </c>
+      <c r="F24" s="14">
+        <v>150</v>
+      </c>
+      <c r="G24" s="14">
+        <v>3</v>
+      </c>
+      <c r="H24" s="14">
+        <v>650</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
@@ -2888,11 +2950,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2910,11 +2972,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2932,11 +2994,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2954,11 +3016,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2976,11 +3038,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2998,11 +3060,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3020,11 +3082,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3042,11 +3104,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3064,11 +3126,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3086,11 +3148,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3108,11 +3170,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3130,11 +3192,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3152,11 +3214,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3174,11 +3236,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3196,11 +3258,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3218,11 +3280,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3240,11 +3302,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3262,11 +3324,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3284,11 +3346,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3306,11 +3368,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3328,11 +3390,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3350,11 +3412,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3372,11 +3434,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3394,11 +3456,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3416,11 +3478,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3438,11 +3500,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3460,11 +3522,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3482,11 +3544,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3504,11 +3566,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3526,11 +3588,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3548,11 +3610,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3570,11 +3632,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3592,11 +3654,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3614,11 +3676,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3636,11 +3698,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3658,11 +3720,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3680,11 +3742,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3702,11 +3764,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3724,11 +3786,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3746,11 +3808,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3768,11 +3830,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3790,11 +3852,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3812,11 +3874,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3834,11 +3896,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3856,11 +3918,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3878,11 +3940,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3900,11 +3962,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3922,11 +3984,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3944,11 +4006,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3966,11 +4028,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3988,11 +4050,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4010,11 +4072,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4032,11 +4094,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4054,11 +4116,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4076,11 +4138,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4098,11 +4160,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4120,11 +4182,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4142,11 +4204,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4164,11 +4226,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4186,11 +4248,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4208,11 +4270,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4230,11 +4292,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4252,11 +4314,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4274,11 +4336,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4296,11 +4358,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4318,11 +4380,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4340,11 +4402,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4362,11 +4424,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4384,11 +4446,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4406,11 +4468,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4428,11 +4490,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4450,11 +4512,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4472,11 +4534,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4494,11 +4556,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4516,11 +4578,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4538,11 +4600,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4560,11 +4622,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4582,11 +4644,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4604,11 +4666,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4626,11 +4688,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4648,11 +4710,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4670,11 +4732,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4692,11 +4754,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4714,11 +4776,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4736,11 +4798,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4758,11 +4820,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4780,11 +4842,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4802,11 +4864,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4824,11 +4886,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4846,11 +4908,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4868,11 +4930,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4890,11 +4952,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4912,11 +4974,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4934,11 +4996,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4956,11 +5018,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4978,11 +5040,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5000,11 +5062,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5022,11 +5084,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5044,11 +5106,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5066,11 +5128,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5088,11 +5150,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5110,11 +5172,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5132,11 +5194,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5154,11 +5216,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5176,11 +5238,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5198,11 +5260,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5220,11 +5282,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5242,11 +5304,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5264,11 +5326,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5286,11 +5348,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5308,11 +5370,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5330,11 +5392,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5352,11 +5414,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5374,11 +5436,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5396,11 +5458,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5418,11 +5480,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5440,11 +5502,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5462,11 +5524,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5484,11 +5546,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5506,11 +5568,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5528,11 +5590,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5550,11 +5612,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5572,11 +5634,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5594,11 +5656,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5616,11 +5678,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5638,11 +5700,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5660,11 +5722,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5682,11 +5744,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5704,11 +5766,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5726,11 +5788,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5748,11 +5810,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5770,11 +5832,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5792,11 +5854,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5814,11 +5876,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5836,11 +5898,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5858,11 +5920,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5880,11 +5942,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5902,11 +5964,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5924,11 +5986,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5946,11 +6008,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5968,11 +6030,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5990,11 +6052,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6012,11 +6074,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6034,11 +6096,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6056,11 +6118,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6078,11 +6140,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6100,11 +6162,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6122,11 +6184,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6144,11 +6206,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6166,11 +6228,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6188,11 +6250,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6210,11 +6272,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6232,11 +6294,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6254,11 +6316,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6276,11 +6338,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6298,11 +6360,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6320,11 +6382,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6342,11 +6404,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6364,11 +6426,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6386,11 +6448,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6408,11 +6470,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6430,11 +6492,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6452,11 +6514,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6474,11 +6536,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6496,11 +6558,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6518,11 +6580,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6540,11 +6602,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6562,11 +6624,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6584,11 +6646,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6606,11 +6668,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6628,11 +6690,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6650,11 +6712,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6672,11 +6734,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6694,11 +6756,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6716,11 +6778,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6738,11 +6800,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6760,11 +6822,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6782,11 +6844,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6804,11 +6866,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6826,11 +6888,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6848,11 +6910,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6870,11 +6932,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6892,11 +6954,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6914,11 +6976,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6936,11 +6998,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6958,11 +7020,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6980,11 +7042,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7002,11 +7064,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7024,11 +7086,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7046,11 +7108,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7068,11 +7130,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7090,11 +7152,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7112,11 +7174,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7134,11 +7196,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7156,11 +7218,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7178,11 +7240,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7200,11 +7262,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7222,11 +7284,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7244,11 +7306,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7266,11 +7328,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7288,11 +7350,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7310,11 +7372,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7332,11 +7394,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7354,11 +7416,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7376,11 +7438,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7398,11 +7460,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7420,11 +7482,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7442,11 +7504,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7464,11 +7526,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7486,11 +7548,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7508,11 +7570,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7530,11 +7592,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7552,11 +7614,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7574,11 +7636,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7596,11 +7658,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7618,11 +7680,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7640,11 +7702,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7662,11 +7724,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7684,11 +7746,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7706,11 +7768,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7728,11 +7790,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7750,11 +7812,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7772,11 +7834,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7794,11 +7856,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7816,11 +7878,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7838,11 +7900,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7860,11 +7922,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7882,11 +7944,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7904,11 +7966,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7926,11 +7988,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7948,11 +8010,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7970,11 +8032,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7992,11 +8054,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8014,11 +8076,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8036,11 +8098,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8058,11 +8120,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8080,11 +8142,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8102,11 +8164,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8124,11 +8186,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8146,11 +8208,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8168,11 +8230,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8190,11 +8252,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8212,11 +8274,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8234,11 +8296,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8256,11 +8318,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8278,11 +8340,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8300,11 +8362,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8322,11 +8384,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8344,11 +8406,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8366,11 +8428,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8388,11 +8450,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8410,11 +8472,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8432,11 +8494,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8454,11 +8516,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8476,11 +8538,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8498,11 +8560,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8520,11 +8582,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8542,11 +8604,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8564,11 +8626,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8586,11 +8648,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8608,11 +8670,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8630,11 +8692,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8652,11 +8714,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8674,11 +8736,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8696,11 +8758,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8718,11 +8780,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8740,11 +8802,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8762,11 +8824,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8784,11 +8846,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8806,11 +8868,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8828,11 +8890,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8850,11 +8912,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8872,11 +8934,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8894,11 +8956,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8916,11 +8978,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8938,11 +9000,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8960,11 +9022,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8982,11 +9044,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9004,11 +9066,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9026,11 +9088,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9048,11 +9110,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9070,11 +9132,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9092,11 +9154,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9114,11 +9176,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9136,11 +9198,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9158,11 +9220,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9180,11 +9242,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9202,11 +9264,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9224,11 +9286,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9246,11 +9308,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9268,11 +9330,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9290,11 +9352,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9312,11 +9374,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9334,11 +9396,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9356,11 +9418,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9378,11 +9440,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9400,11 +9462,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9422,11 +9484,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9444,11 +9506,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9466,11 +9528,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9488,11 +9550,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9510,11 +9572,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9532,11 +9594,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9554,11 +9616,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9576,11 +9638,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9598,11 +9660,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9620,11 +9682,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9642,11 +9704,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9664,11 +9726,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9686,11 +9748,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9708,11 +9770,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9730,11 +9792,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9752,11 +9814,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9774,11 +9836,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9796,11 +9858,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9818,11 +9880,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9840,11 +9902,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9862,11 +9924,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9884,11 +9946,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9906,11 +9968,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9928,11 +9990,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9950,11 +10012,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9972,11 +10034,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9994,11 +10056,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10016,11 +10078,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10038,11 +10100,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10060,11 +10122,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10082,11 +10144,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10104,11 +10166,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10126,11 +10188,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10148,11 +10210,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10170,11 +10232,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -10191,8 +10253,13 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J22 J24:J401">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492AE04F-274D-4D30-8F4C-63323E490B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{492AE04F-274D-4D30-8F4C-63323E490B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B746B25-9BD2-4AF4-BB50-A9451786AC0B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>It was a good Day</t>
+  </si>
+  <si>
+    <t>Was having a Headache</t>
+  </si>
+  <si>
+    <t>Gone for shopping</t>
   </si>
 </sst>
 </file>
@@ -1940,73 +1946,139 @@
       <c r="A25" s="8">
         <v>46268</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>129</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>360</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1239</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>201</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>46269</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>45</v>
+      </c>
+      <c r="E26" s="14">
+        <v>12</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>480</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1287</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>153</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>46270</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="B27" s="14">
+        <v>600</v>
+      </c>
+      <c r="C27" s="14">
+        <v>115</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>19</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>500</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1294</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>146</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{492AE04F-274D-4D30-8F4C-63323E490B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B746B25-9BD2-4AF4-BB50-A9451786AC0B}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{492AE04F-274D-4D30-8F4C-63323E490B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{529BEFE2-7629-4E4A-89FB-C84B1F7501B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Gone for shopping</t>
+  </si>
+  <si>
+    <t>Tomorrow we have a CA</t>
   </si>
 </sst>
 </file>
@@ -2084,25 +2087,47 @@
       <c r="A28" s="8">
         <v>46271</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>468</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1068</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>372</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{492AE04F-274D-4D30-8F4C-63323E490B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{529BEFE2-7629-4E4A-89FB-C84B1F7501B3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352D85DF-B0F4-4805-8CEE-C593BA84D870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>Tomorrow we have a CA</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Today was my Brother's Roka</t>
   </si>
 </sst>
 </file>
@@ -2133,25 +2139,47 @@
       <c r="A29" s="8">
         <v>46272</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>15</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>650</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1225</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>215</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352D85DF-B0F4-4805-8CEE-C593BA84D870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{352D85DF-B0F4-4805-8CEE-C593BA84D870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E495962-3488-4F90-BABB-72E474E0EB23}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>Today was my Brother's Roka</t>
+  </si>
+  <si>
+    <t>Was really Tired</t>
+  </si>
+  <si>
+    <t>Wasn't able to go to class due to protest</t>
   </si>
 </sst>
 </file>
@@ -2185,74 +2191,144 @@
       <c r="A30" s="8">
         <v>46273</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="B30" s="14">
+        <v>400</v>
+      </c>
+      <c r="C30" s="14">
+        <v>120</v>
+      </c>
+      <c r="D30" s="14">
+        <v>30</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>400</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>46274</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="B31" s="14">
+        <v>620</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>45</v>
+      </c>
+      <c r="E31" s="14">
+        <v>25</v>
+      </c>
+      <c r="F31" s="14">
+        <v>150</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3</v>
+      </c>
+      <c r="H31" s="14">
+        <v>300</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>180</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="14">
+        <v>410</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60</v>
+      </c>
+      <c r="E32" s="14">
+        <v>25</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>500</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
+      <c r="A33" s="8">
+        <v>46276</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
@@ -2274,7 +2350,9 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
+      <c r="A34" s="8">
+        <v>46277</v>
+      </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{352D85DF-B0F4-4805-8CEE-C593BA84D870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E495962-3488-4F90-BABB-72E474E0EB23}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE933B-D117-4F05-BAF0-4470E838CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>Wasn't able to go to class due to protest</t>
+  </si>
+  <si>
+    <t>Was Studying for CA then went to Amritsar wth family</t>
   </si>
 </sst>
 </file>
@@ -2325,29 +2328,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46276</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="B33" s="14">
+        <v>240</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>4</v>
+      </c>
+      <c r="G33" s="14">
+        <v>200</v>
+      </c>
+      <c r="H33" s="14">
+        <v>800</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1164</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>276</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE933B-D117-4F05-BAF0-4470E838CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DACE933B-D117-4F05-BAF0-4470E838CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFA27C80-4CB0-4623-8D07-C371F0D0D9A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Was Studying for CA then went to Amritsar wth family</t>
+  </si>
+  <si>
+    <t>Was feeling low</t>
   </si>
 </sst>
 </file>
@@ -2378,50 +2381,98 @@
       <c r="A34" s="8">
         <v>46277</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>120</v>
+      </c>
+      <c r="D34" s="14">
+        <v>15</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>400</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>485</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>60</v>
+      </c>
+      <c r="E35" s="14">
+        <v>25</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>540</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
+      <c r="A36" s="8">
+        <v>46279</v>
+      </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -2443,7 +2494,9 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
+      <c r="A37" s="8">
+        <v>46280</v>
+      </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -2465,7 +2518,9 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+      <c r="A38" s="8">
+        <v>46281</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2487,7 +2542,9 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
+      <c r="A39" s="8">
+        <v>46282</v>
+      </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -2509,7 +2566,9 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
+      <c r="A40" s="8">
+        <v>46283</v>
+      </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -2531,7 +2590,9 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
+      <c r="A41" s="8">
+        <v>46284</v>
+      </c>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -2553,7 +2614,9 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
+      <c r="A42" s="8">
+        <v>46285</v>
+      </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DACE933B-D117-4F05-BAF0-4470E838CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFA27C80-4CB0-4623-8D07-C371F0D0D9A5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D3DA5A-3880-4C72-AEA2-487D7944827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Was feeling low</t>
+  </si>
+  <si>
+    <t>Hectic Day</t>
   </si>
 </sst>
 </file>
@@ -2348,21 +2351,21 @@
         <v>0</v>
       </c>
       <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
         <v>4</v>
-      </c>
-      <c r="G33" s="14">
-        <v>200</v>
       </c>
       <c r="H33" s="14">
         <v>800</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1164</v>
+        <v>1360</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>61</v>
@@ -2474,72 +2477,134 @@
         <v>46279</v>
       </c>
       <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="C36" s="14">
+        <v>120</v>
+      </c>
+      <c r="D36" s="14">
+        <v>20</v>
+      </c>
+      <c r="E36" s="14">
+        <v>40</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>460</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46280</v>
       </c>
       <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="C37" s="14">
+        <v>125</v>
+      </c>
+      <c r="D37" s="14">
+        <v>45</v>
+      </c>
+      <c r="E37" s="14">
+        <v>15</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>550</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>985</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>455</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46281</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="B38" s="14">
+        <v>426</v>
+      </c>
+      <c r="C38" s="14">
+        <v>136</v>
+      </c>
+      <c r="D38" s="14">
+        <v>15</v>
+      </c>
+      <c r="E38" s="14">
+        <v>50</v>
+      </c>
+      <c r="F38" s="14">
+        <v>100</v>
+      </c>
+      <c r="G38" s="14">
+        <v>2</v>
+      </c>
+      <c r="H38" s="14">
+        <v>265</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>992</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>448</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D3DA5A-3880-4C72-AEA2-487D7944827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Hectic Day</t>
+  </si>
+  <si>
+    <t>Today,met my School Friends</t>
   </si>
 </sst>
 </file>
@@ -2476,7 +2479,9 @@
       <c r="A36" s="8">
         <v>46279</v>
       </c>
-      <c r="B36" s="14"/>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
       <c r="C36" s="14">
         <v>120</v>
       </c>
@@ -2497,11 +2502,11 @@
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>1260</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>57</v>
@@ -2520,7 +2525,9 @@
       <c r="A37" s="8">
         <v>46280</v>
       </c>
-      <c r="B37" s="14"/>
+      <c r="B37" s="14">
+        <v>360</v>
+      </c>
       <c r="C37" s="14">
         <v>125</v>
       </c>
@@ -2541,11 +2548,11 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>985</v>
+        <v>1345</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>455</v>
+        <v>95</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>57</v>
@@ -2610,25 +2617,47 @@
       <c r="A39" s="8">
         <v>46282</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="B39" s="14">
+        <v>379</v>
+      </c>
+      <c r="C39" s="14">
+        <v>136</v>
+      </c>
+      <c r="D39" s="14">
+        <v>30</v>
+      </c>
+      <c r="E39" s="14">
+        <v>40</v>
+      </c>
+      <c r="F39" s="14">
+        <v>300</v>
+      </c>
+      <c r="G39" s="14">
+        <v>6</v>
+      </c>
+      <c r="H39" s="14">
+        <v>360</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>195</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEF2DF66-CED8-4316-BFB8-1B0D4CCD2356}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>Today,met my School Friends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Had a CA tomorrow </t>
   </si>
 </sst>
 </file>
@@ -2663,25 +2666,47 @@
       <c r="A40" s="8">
         <v>46283</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>120</v>
+      </c>
+      <c r="D40" s="14">
+        <v>60</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEF2DF66-CED8-4316-BFB8-1B0D4CCD2356}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4A4EECB-9861-4D31-AC2F-0F533C683300}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2712,24 +2712,44 @@
       <c r="A41" s="8">
         <v>46284</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="B41" s="14">
+        <v>360</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>30</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>150</v>
+      </c>
+      <c r="G41" s="14">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14">
+        <v>600</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4A4EECB-9861-4D31-AC2F-0F533C683300}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B2DB44E-91B3-4C52-9443-749FFD8F70B7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2713,7 +2713,7 @@
         <v>46284</v>
       </c>
       <c r="B41" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C41" s="14">
         <v>0</v>
@@ -2735,11 +2735,11 @@
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1200</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>58</v>
@@ -2750,31 +2750,55 @@
       <c r="M41" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N41" s="17"/>
+      <c r="N41" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>46285</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="B42" s="14">
+        <v>360</v>
+      </c>
+      <c r="C42" s="14">
+        <v>120</v>
+      </c>
+      <c r="D42" s="14">
+        <v>30</v>
+      </c>
+      <c r="E42" s="14">
+        <v>15</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>450</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B2DB44E-91B3-4C52-9443-749FFD8F70B7}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B19B57B1-9506-4445-9CC7-42808CCF486E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2801,29 +2801,55 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="14">
+        <v>380</v>
+      </c>
+      <c r="C43" s="14">
+        <v>120</v>
+      </c>
+      <c r="D43" s="14">
+        <v>60</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>200</v>
+      </c>
+      <c r="G43" s="14">
+        <v>4</v>
+      </c>
+      <c r="H43" s="14">
+        <v>420</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
+      <c r="A44" s="8">
+        <v>46287</v>
+      </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -2845,7 +2871,9 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
+      <c r="A45" s="8">
+        <v>46288</v>
+      </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -2867,7 +2895,9 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
+      <c r="A46" s="8">
+        <v>46289</v>
+      </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2889,7 +2919,9 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
+      <c r="A47" s="8">
+        <v>46290</v>
+      </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2911,7 +2943,9 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
+      <c r="A48" s="8">
+        <v>46291</v>
+      </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2933,7 +2967,9 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
+      <c r="A49" s="8">
+        <v>46292</v>
+      </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2955,7 +2991,9 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
+      <c r="A50" s="8">
+        <v>46293</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2977,7 +3015,9 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
+      <c r="A51" s="8">
+        <v>46294</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2999,7 +3039,9 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
+      <c r="A52" s="8">
+        <v>46295</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -3021,7 +3063,9 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
+      <c r="A53" s="8">
+        <v>46296</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -3043,7 +3087,9 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
+      <c r="A54" s="8">
+        <v>46297</v>
+      </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B19B57B1-9506-4445-9CC7-42808CCF486E}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EBAB3B8-09CB-41DF-8084-FAFD80A8AD1F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t xml:space="preserve">Had a CA tomorrow </t>
+  </si>
+  <si>
+    <t>Was with my frineds</t>
   </si>
 </sst>
 </file>
@@ -2850,49 +2853,93 @@
       <c r="A44" s="8">
         <v>46287</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="B44" s="14">
+        <v>360</v>
+      </c>
+      <c r="C44" s="14">
+        <v>135</v>
+      </c>
+      <c r="D44" s="14">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>350</v>
+      </c>
+      <c r="G44" s="14">
+        <v>7</v>
+      </c>
+      <c r="H44" s="14">
+        <v>250</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>255</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>46288</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="B45" s="14">
+        <v>420</v>
+      </c>
+      <c r="C45" s="14">
+        <v>155</v>
+      </c>
+      <c r="D45" s="14">
+        <v>15</v>
+      </c>
+      <c r="E45" s="14">
+        <v>15</v>
+      </c>
+      <c r="F45" s="14">
+        <v>200</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4</v>
+      </c>
+      <c r="H45" s="14">
+        <v>420</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1225</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>215</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EBAB3B8-09CB-41DF-8084-FAFD80A8AD1F}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A4D5D2-C7CE-436C-A389-54FFA4BF6E49}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>Was with my frineds</t>
+  </si>
+  <si>
+    <t>Was working on Project</t>
+  </si>
+  <si>
+    <t>Have a CA tomorrw</t>
   </si>
 </sst>
 </file>
@@ -2945,49 +2951,93 @@
       <c r="A46" s="8">
         <v>46289</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="B46" s="14">
+        <v>425</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>60</v>
+      </c>
+      <c r="E46" s="14">
+        <v>30</v>
+      </c>
+      <c r="F46" s="14">
+        <v>300</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6</v>
+      </c>
+      <c r="H46" s="14">
+        <v>300</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1115</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>325</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46290</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="B47" s="14">
+        <v>389</v>
+      </c>
+      <c r="C47" s="14">
+        <v>120</v>
+      </c>
+      <c r="D47" s="14">
+        <v>30</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>350</v>
+      </c>
+      <c r="G47" s="14">
+        <v>7</v>
+      </c>
+      <c r="H47" s="14">
+        <v>200</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1149</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>291</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A4D5D2-C7CE-436C-A389-54FFA4BF6E49}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50DAF932-8307-48AA-BD97-F3B254BC025E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3043,25 +3043,47 @@
       <c r="A48" s="8">
         <v>46291</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="B48" s="14">
+        <v>700</v>
+      </c>
+      <c r="C48" s="14">
+        <v>75</v>
+      </c>
+      <c r="D48" s="14">
+        <v>75</v>
+      </c>
+      <c r="E48" s="14">
+        <v>45</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>400</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>145</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
@@ -10875,6 +10897,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{FE83B28A-B66B-4911-B628-8C1A290C32A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50DAF932-8307-48AA-BD97-F3B254BC025E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,15 @@
   </si>
   <si>
     <t>Have a CA tomorrw</t>
+  </si>
+  <si>
+    <t>Finding Course for 10 days</t>
+  </si>
+  <si>
+    <t>Enjoying Sunday</t>
+  </si>
+  <si>
+    <t>Planning for tomorrow</t>
   </si>
 </sst>
 </file>
@@ -3089,73 +3098,139 @@
       <c r="A49" s="8">
         <v>46292</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="B49" s="14">
+        <v>468</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>480</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>948</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>492</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46293</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="B50" s="14">
+        <v>480</v>
+      </c>
+      <c r="C50" s="14">
+        <v>120</v>
+      </c>
+      <c r="D50" s="14">
+        <v>60</v>
+      </c>
+      <c r="E50" s="14">
+        <v>45</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>420</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>315</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>46294</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="B51" s="14">
+        <v>540</v>
+      </c>
+      <c r="C51" s="14">
+        <v>120</v>
+      </c>
+      <c r="D51" s="14">
+        <v>35</v>
+      </c>
+      <c r="E51" s="14">
+        <v>45</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>500</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6E1E189-BD68-454D-B05D-EC3CC4EA9C18}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>Planning for tomorrow</t>
+  </si>
+  <si>
+    <t>Was at birthday</t>
+  </si>
+  <si>
+    <t>Was tired because of tomorrow</t>
   </si>
 </sst>
 </file>
@@ -3236,49 +3242,93 @@
       <c r="A52" s="8">
         <v>46295</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="B52" s="14">
+        <v>680</v>
+      </c>
+      <c r="C52" s="14">
+        <v>120</v>
+      </c>
+      <c r="D52" s="14">
+        <v>60</v>
+      </c>
+      <c r="E52" s="14">
+        <v>45</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>450</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>85</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>46296</v>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="B53" s="14">
+        <v>750</v>
+      </c>
+      <c r="C53" s="14">
+        <v>120</v>
+      </c>
+      <c r="D53" s="14">
+        <v>30</v>
+      </c>
+      <c r="E53" s="14">
+        <v>15</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>500</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1415</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>25</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6E1E189-BD68-454D-B05D-EC3CC4EA9C18}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA374DDC-2BD9-4CEB-8044-C7580CE61BC3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,15 @@
   </si>
   <si>
     <t>Was tired because of tomorrow</t>
+  </si>
+  <si>
+    <t>Trying to learn new skills</t>
+  </si>
+  <si>
+    <t>Was preparing for a Family Event</t>
+  </si>
+  <si>
+    <t>Today was event</t>
   </si>
 </sst>
 </file>
@@ -3334,72 +3343,142 @@
       <c r="A54" s="8">
         <v>46297</v>
       </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="B54" s="14">
+        <v>670</v>
+      </c>
+      <c r="C54" s="14">
+        <v>135</v>
+      </c>
+      <c r="D54" s="14">
+        <v>60</v>
+      </c>
+      <c r="E54" s="14">
+        <v>45</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>180</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+        <v>350</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B55" s="14">
+        <v>780</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>600</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+      <c r="A56" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B56" s="14">
+        <v>360</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
       <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>1080</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
+      <c r="A57" s="8">
+        <v>46300</v>
+      </c>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -3421,7 +3500,9 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
+      <c r="A58" s="8">
+        <v>46301</v>
+      </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -3443,7 +3524,9 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
+      <c r="A59" s="8">
+        <v>46302</v>
+      </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA374DDC-2BD9-4CEB-8044-C7580CE61BC3}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B370A35A-397E-459A-8382-47BC46AF4423}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Today was event</t>
+  </si>
+  <si>
+    <t>Was tired</t>
   </si>
 </sst>
 </file>
@@ -3453,14 +3456,16 @@
       <c r="G56" s="14">
         <v>0</v>
       </c>
-      <c r="H56" s="14"/>
+      <c r="H56" s="14">
+        <v>600</v>
+      </c>
       <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>960</v>
       </c>
       <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>480</v>
       </c>
       <c r="K56" s="16" t="s">
         <v>61</v>
@@ -3479,25 +3484,47 @@
       <c r="A57" s="8">
         <v>46300</v>
       </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="B57" s="14">
+        <v>548</v>
+      </c>
+      <c r="C57" s="14">
+        <v>120</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>150</v>
+      </c>
+      <c r="G57" s="14">
+        <v>3</v>
+      </c>
+      <c r="H57" s="14">
+        <v>450</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1268</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>172</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B370A35A-397E-459A-8382-47BC46AF4423}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0D53126-67B6-43E6-9FD0-8E433EEBFE10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>Was tired</t>
+  </si>
+  <si>
+    <t>Was Hectic Day</t>
   </si>
 </sst>
 </file>
@@ -3497,21 +3500,21 @@
         <v>0</v>
       </c>
       <c r="F57" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G57" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H57" s="14">
         <v>450</v>
       </c>
       <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v>1268</v>
+        <v>1318</v>
       </c>
       <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="K57" s="16" t="s">
         <v>58</v>
@@ -3530,52 +3533,98 @@
       <c r="A58" s="8">
         <v>46301</v>
       </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="B58" s="14">
+        <v>500</v>
+      </c>
+      <c r="C58" s="14">
+        <v>135</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>350</v>
+      </c>
+      <c r="G58" s="14">
+        <v>7</v>
+      </c>
+      <c r="H58" s="14">
+        <v>250</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>205</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>46302</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="B59" s="14">
+        <v>480</v>
+      </c>
+      <c r="C59" s="14">
+        <v>120</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>150</v>
+      </c>
+      <c r="G59" s="14">
+        <v>3</v>
+      </c>
+      <c r="H59" s="14">
+        <v>400</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
+      <c r="A60" s="8">
+        <v>46303</v>
+      </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{5080E267-15C8-4CBE-9175-D19D1A0C00E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0D53126-67B6-43E6-9FD0-8E433EEBFE10}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{48DBF6EC-9206-4982-9F07-387BE0D50DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Was Hectic Day</t>
+  </si>
+  <si>
+    <t>Was out with frineds</t>
   </si>
 </sst>
 </file>
@@ -3625,47 +3628,93 @@
       <c r="A60" s="8">
         <v>46303</v>
       </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="B60" s="14">
+        <v>500</v>
+      </c>
+      <c r="C60" s="14">
+        <v>136</v>
+      </c>
+      <c r="D60" s="14">
+        <v>45</v>
+      </c>
+      <c r="E60" s="14">
+        <v>15</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>450</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1146</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>294</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B61" s="14">
+        <v>456</v>
+      </c>
+      <c r="C61" s="14">
+        <v>120</v>
+      </c>
+      <c r="D61" s="14">
+        <v>60</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>360</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>996</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>444</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{48DBF6EC-9206-4982-9F07-387BE0D50DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8ED45B-7711-4B2E-98CB-BBB2443FC4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Was out with frineds</t>
+  </si>
+  <si>
+    <t>Was Studying for MTT</t>
   </si>
 </sst>
 </file>
@@ -3717,51 +3720,101 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B62" s="14">
+        <v>600</v>
+      </c>
+      <c r="C62" s="14">
+        <v>60</v>
+      </c>
+      <c r="D62" s="14">
+        <v>60</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>536</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1256</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>184</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+      <c r="A63" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B63" s="14">
+        <v>780</v>
+      </c>
+      <c r="C63" s="14">
+        <v>0</v>
+      </c>
+      <c r="D63" s="14">
+        <v>120</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>304</v>
+      </c>
+      <c r="I63" s="15">
+        <f t="shared" ref="I63" si="4">IF(SUM(B63:F63,H63)=0,"",SUM(B63:F63,H63))</f>
+        <v>1204</v>
+      </c>
+      <c r="J63" s="15">
+        <f t="shared" ref="J63" si="5">IF(I63="","",1440-I63)</f>
+        <v>236</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
+      <c r="A64" s="8">
+        <v>46307</v>
+      </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3783,7 +3836,9 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
+      <c r="A65" s="8">
+        <v>46308</v>
+      </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3805,7 +3860,9 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+      <c r="A66" s="8">
+        <v>46309</v>
+      </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3827,7 +3884,9 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
+      <c r="A67" s="8">
+        <v>46310</v>
+      </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3849,7 +3908,9 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
+      <c r="A68" s="8">
+        <v>46311</v>
+      </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3871,7 +3932,9 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
+      <c r="A69" s="8">
+        <v>46312</v>
+      </c>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -3893,7 +3956,9 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
+      <c r="A70" s="8">
+        <v>46313</v>
+      </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -3902,11 +3967,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3915,7 +3980,9 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
+      <c r="A71" s="8">
+        <v>46314</v>
+      </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3924,11 +3991,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3937,7 +4004,9 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
+      <c r="A72" s="8">
+        <v>46315</v>
+      </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3946,11 +4015,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3968,11 +4037,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3990,11 +4059,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -4012,11 +4081,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -4034,11 +4103,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -4056,11 +4125,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -4078,11 +4147,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -4100,11 +4169,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -4122,11 +4191,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -4144,11 +4213,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -4166,11 +4235,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -4188,11 +4257,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -4210,11 +4279,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -4232,11 +4301,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -4254,11 +4323,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -4276,11 +4345,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -4298,11 +4367,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -4320,11 +4389,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -4342,11 +4411,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -4364,11 +4433,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4386,11 +4455,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4408,11 +4477,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4430,11 +4499,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4452,11 +4521,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4474,11 +4543,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4496,11 +4565,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4518,11 +4587,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4540,11 +4609,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4562,11 +4631,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4584,11 +4653,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4606,11 +4675,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4628,11 +4697,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4650,11 +4719,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4672,11 +4741,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4694,11 +4763,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4716,11 +4785,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4738,11 +4807,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4760,11 +4829,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4782,11 +4851,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4804,11 +4873,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4826,11 +4895,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4848,11 +4917,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4870,11 +4939,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4892,11 +4961,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4914,11 +4983,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4936,11 +5005,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4958,11 +5027,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4980,11 +5049,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -5002,11 +5071,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -5024,11 +5093,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -5046,11 +5115,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -5068,11 +5137,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -5090,11 +5159,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -5112,11 +5181,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -5134,11 +5203,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -5156,11 +5225,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -5178,11 +5247,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -5200,11 +5269,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5222,11 +5291,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -5244,11 +5313,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -5266,11 +5335,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -5288,11 +5357,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5310,11 +5379,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5332,11 +5401,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5354,11 +5423,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5376,11 +5445,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5398,11 +5467,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5420,11 +5489,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5442,11 +5511,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5464,11 +5533,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5486,11 +5555,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5508,11 +5577,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5530,11 +5599,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5552,11 +5621,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5574,11 +5643,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5596,11 +5665,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5618,11 +5687,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5640,11 +5709,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5662,11 +5731,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5684,11 +5753,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5706,11 +5775,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5728,11 +5797,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5750,11 +5819,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5772,11 +5841,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5794,11 +5863,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5816,11 +5885,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5838,11 +5907,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5860,11 +5929,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5882,11 +5951,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5904,11 +5973,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5926,11 +5995,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5948,11 +6017,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5970,11 +6039,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5992,11 +6061,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -6014,11 +6083,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -6036,11 +6105,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -6058,11 +6127,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -6080,11 +6149,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -6102,11 +6171,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -6124,11 +6193,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -6146,11 +6215,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -6168,11 +6237,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -6190,11 +6259,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -6212,11 +6281,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -6234,11 +6303,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -6256,11 +6325,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6278,11 +6347,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6300,11 +6369,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6322,11 +6391,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6344,11 +6413,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6366,11 +6435,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6388,11 +6457,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6410,11 +6479,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6432,11 +6501,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6454,11 +6523,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6476,11 +6545,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6498,11 +6567,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6520,11 +6589,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6542,11 +6611,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6564,11 +6633,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6586,11 +6655,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6608,11 +6677,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6630,11 +6699,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6652,11 +6721,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6674,11 +6743,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6696,11 +6765,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6718,11 +6787,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6740,11 +6809,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6762,11 +6831,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6784,11 +6853,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6806,11 +6875,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6828,11 +6897,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6850,11 +6919,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6872,11 +6941,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6894,11 +6963,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6916,11 +6985,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6938,11 +7007,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6960,11 +7029,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6982,11 +7051,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -7004,11 +7073,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -7026,11 +7095,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -7048,11 +7117,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -7070,11 +7139,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -7092,11 +7161,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -7114,11 +7183,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -7136,11 +7205,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -7158,11 +7227,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -7180,11 +7249,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -7202,11 +7271,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -7224,11 +7293,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7246,11 +7315,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7268,11 +7337,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7290,11 +7359,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7312,11 +7381,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7334,11 +7403,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7356,11 +7425,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7378,11 +7447,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7400,11 +7469,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7422,11 +7491,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7444,11 +7513,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7466,11 +7535,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7488,11 +7557,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7510,11 +7579,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7532,11 +7601,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7554,11 +7623,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7576,11 +7645,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7598,11 +7667,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7620,11 +7689,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7642,11 +7711,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7664,11 +7733,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7686,11 +7755,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7708,11 +7777,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7730,11 +7799,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7752,11 +7821,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7774,11 +7843,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7796,11 +7865,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7818,11 +7887,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7840,11 +7909,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7862,11 +7931,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7884,11 +7953,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7906,11 +7975,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7928,11 +7997,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7950,11 +8019,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7972,11 +8041,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7994,11 +8063,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -8016,11 +8085,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8038,11 +8107,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -8060,11 +8129,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -8082,11 +8151,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -8104,11 +8173,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -8126,11 +8195,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8148,11 +8217,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8170,11 +8239,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8192,11 +8261,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8214,11 +8283,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8236,11 +8305,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -8258,11 +8327,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8280,11 +8349,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8302,11 +8371,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8324,11 +8393,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8346,11 +8415,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8368,11 +8437,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8390,11 +8459,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8412,11 +8481,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8434,11 +8503,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8456,11 +8525,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8478,11 +8547,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8500,11 +8569,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8522,11 +8591,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8544,11 +8613,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8566,11 +8635,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8588,11 +8657,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8610,11 +8679,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8632,11 +8701,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8654,11 +8723,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8676,11 +8745,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8698,11 +8767,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8720,11 +8789,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8742,11 +8811,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8764,11 +8833,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8786,11 +8855,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8808,11 +8877,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8830,11 +8899,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8852,11 +8921,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8874,11 +8943,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8896,11 +8965,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8918,11 +8987,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8940,11 +9009,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8962,11 +9031,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8984,11 +9053,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -9006,11 +9075,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -9028,11 +9097,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -9050,11 +9119,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -9072,11 +9141,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -9094,11 +9163,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -9116,11 +9185,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -9138,11 +9207,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -9160,11 +9229,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -9182,11 +9251,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -9204,11 +9273,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -9226,11 +9295,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -9248,11 +9317,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9270,11 +9339,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9292,11 +9361,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9314,11 +9383,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9336,11 +9405,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9358,11 +9427,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9380,11 +9449,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9402,11 +9471,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9424,11 +9493,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9446,11 +9515,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9468,11 +9537,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9490,11 +9559,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9512,11 +9581,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9534,11 +9603,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9556,11 +9625,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9578,11 +9647,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9600,11 +9669,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9622,11 +9691,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9644,11 +9713,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9666,11 +9735,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9688,11 +9757,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9710,11 +9779,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9732,11 +9801,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9754,11 +9823,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9776,11 +9845,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9798,11 +9867,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9820,11 +9889,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9842,11 +9911,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9864,11 +9933,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9886,11 +9955,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9908,11 +9977,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9930,11 +9999,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9952,11 +10021,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9974,11 +10043,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9996,11 +10065,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -10018,11 +10087,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -10040,11 +10109,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -10062,11 +10131,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -10084,11 +10153,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -10106,11 +10175,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -10128,11 +10197,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -10150,11 +10219,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -10172,11 +10241,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -10194,11 +10263,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -10216,11 +10285,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -10238,11 +10307,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -10260,11 +10329,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10282,11 +10351,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10304,11 +10373,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10326,11 +10395,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10348,11 +10417,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10370,11 +10439,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10392,11 +10461,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10414,11 +10483,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10436,11 +10505,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10458,11 +10527,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10480,11 +10549,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10502,11 +10571,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10524,11 +10593,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10546,11 +10615,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10568,11 +10637,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10590,11 +10659,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10612,11 +10681,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10634,11 +10703,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10656,11 +10725,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10678,11 +10747,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10700,11 +10769,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10722,11 +10791,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10744,11 +10813,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10766,11 +10835,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10788,11 +10857,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10810,11 +10879,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10832,11 +10901,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10854,11 +10923,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10876,11 +10945,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10898,11 +10967,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10920,11 +10989,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10942,11 +11011,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10964,11 +11033,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10986,11 +11055,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -11008,11 +11077,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -11030,11 +11099,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -11052,11 +11121,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -11074,11 +11143,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -11096,11 +11165,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -11118,11 +11187,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -11140,11 +11209,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -11162,11 +11231,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -11184,11 +11253,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8ED45B-7711-4B2E-98CB-BBB2443FC4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6B8ED45B-7711-4B2E-98CB-BBB2443FC4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BC68F94-9DFD-4866-967A-BF4D003950C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3799,7 +3799,7 @@
         <v>236</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L63" s="16" t="s">
         <v>57</v>
@@ -3815,25 +3815,47 @@
       <c r="A64" s="8">
         <v>46307</v>
       </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+      <c r="B64" s="14">
+        <v>360</v>
+      </c>
+      <c r="C64" s="14">
+        <v>0</v>
+      </c>
+      <c r="D64" s="14">
+        <v>120</v>
+      </c>
+      <c r="E64" s="14">
+        <v>30</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>450</v>
+      </c>
+      <c r="I64" s="15">
+        <f t="shared" ref="I64" si="6">IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
+        <v>960</v>
+      </c>
+      <c r="J64" s="15">
+        <f t="shared" ref="J64" si="7">IF(I64="","",1440-I64)</f>
+        <v>480</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
@@ -3967,11 +3989,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3991,11 +4013,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -4015,11 +4037,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -4037,11 +4059,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -4059,11 +4081,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -4081,11 +4103,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -4103,11 +4125,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -4125,11 +4147,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -4147,11 +4169,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -4169,11 +4191,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -4191,11 +4213,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -4213,11 +4235,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -4235,11 +4257,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -4257,11 +4279,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -4279,11 +4301,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -4301,11 +4323,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -4323,11 +4345,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -4345,11 +4367,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -4367,11 +4389,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -4389,11 +4411,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -4411,11 +4433,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -4433,11 +4455,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4455,11 +4477,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4477,11 +4499,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4499,11 +4521,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4521,11 +4543,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4543,11 +4565,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4565,11 +4587,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4587,11 +4609,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4609,11 +4631,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4631,11 +4653,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4653,11 +4675,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4675,11 +4697,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4697,11 +4719,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4719,11 +4741,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4741,11 +4763,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4763,11 +4785,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4785,11 +4807,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4807,11 +4829,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4829,11 +4851,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4851,11 +4873,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4873,11 +4895,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4895,11 +4917,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4917,11 +4939,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4939,11 +4961,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4961,11 +4983,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4983,11 +5005,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -5005,11 +5027,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -5027,11 +5049,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -5049,11 +5071,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -5071,11 +5093,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -5093,11 +5115,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -5115,11 +5137,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -5137,11 +5159,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -5159,11 +5181,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -5181,11 +5203,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -5203,11 +5225,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -5225,11 +5247,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -5247,11 +5269,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -5269,11 +5291,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5291,11 +5313,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -5313,11 +5335,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -5335,11 +5357,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -5357,11 +5379,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5379,11 +5401,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5401,11 +5423,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5423,11 +5445,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5445,11 +5467,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5467,11 +5489,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5489,11 +5511,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5511,11 +5533,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5533,11 +5555,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5555,11 +5577,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5577,11 +5599,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5599,11 +5621,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5621,11 +5643,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5643,11 +5665,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5665,11 +5687,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5687,11 +5709,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5709,11 +5731,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5731,11 +5753,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5753,11 +5775,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5775,11 +5797,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5797,11 +5819,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5819,11 +5841,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5841,11 +5863,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5863,11 +5885,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5885,11 +5907,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5907,11 +5929,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5929,11 +5951,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5951,11 +5973,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5973,11 +5995,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5995,11 +6017,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -6017,11 +6039,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -6039,11 +6061,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -6061,11 +6083,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -6083,11 +6105,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -6105,11 +6127,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -6127,11 +6149,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -6149,11 +6171,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -6171,11 +6193,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -6193,11 +6215,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -6215,11 +6237,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -6237,11 +6259,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -6259,11 +6281,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -6281,11 +6303,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -6303,11 +6325,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -6325,11 +6347,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6347,11 +6369,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6369,11 +6391,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6391,11 +6413,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6413,11 +6435,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6435,11 +6457,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6457,11 +6479,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6479,11 +6501,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6501,11 +6523,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6523,11 +6545,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6545,11 +6567,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6567,11 +6589,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6589,11 +6611,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6611,11 +6633,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6633,11 +6655,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6655,11 +6677,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6677,11 +6699,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6699,11 +6721,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6721,11 +6743,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6743,11 +6765,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6765,11 +6787,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6787,11 +6809,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6809,11 +6831,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6831,11 +6853,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6853,11 +6875,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6875,11 +6897,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6897,11 +6919,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6919,11 +6941,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6941,11 +6963,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6963,11 +6985,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6985,11 +7007,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -7007,11 +7029,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -7029,11 +7051,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -7051,11 +7073,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -7073,11 +7095,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -7095,11 +7117,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -7117,11 +7139,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -7139,11 +7161,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -7161,11 +7183,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -7183,11 +7205,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -7205,11 +7227,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -7227,11 +7249,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -7249,11 +7271,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -7271,11 +7293,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -7293,11 +7315,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7315,11 +7337,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7337,11 +7359,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7359,11 +7381,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7381,11 +7403,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7403,11 +7425,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7425,11 +7447,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7447,11 +7469,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7469,11 +7491,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7491,11 +7513,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7513,11 +7535,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7535,11 +7557,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7557,11 +7579,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7579,11 +7601,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7601,11 +7623,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7623,11 +7645,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7645,11 +7667,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7667,11 +7689,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7689,11 +7711,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7711,11 +7733,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7733,11 +7755,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7755,11 +7777,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7777,11 +7799,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7799,11 +7821,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7821,11 +7843,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7843,11 +7865,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7865,11 +7887,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7887,11 +7909,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7909,11 +7931,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7931,11 +7953,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7953,11 +7975,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7975,11 +7997,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7997,11 +8019,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -8019,11 +8041,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -8041,11 +8063,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -8063,11 +8085,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -8085,11 +8107,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8107,11 +8129,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -8129,11 +8151,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -8151,11 +8173,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -8173,11 +8195,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -8195,11 +8217,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8217,11 +8239,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8239,11 +8261,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8261,11 +8283,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8283,11 +8305,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8305,11 +8327,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -8327,11 +8349,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8349,11 +8371,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8371,11 +8393,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8393,11 +8415,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8415,11 +8437,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8437,11 +8459,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8459,11 +8481,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8481,11 +8503,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8503,11 +8525,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8525,11 +8547,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8547,11 +8569,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8569,11 +8591,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8591,11 +8613,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8613,11 +8635,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8635,11 +8657,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8657,11 +8679,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8679,11 +8701,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8701,11 +8723,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8723,11 +8745,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8745,11 +8767,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8767,11 +8789,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8789,11 +8811,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8811,11 +8833,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8833,11 +8855,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8855,11 +8877,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8877,11 +8899,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8899,11 +8921,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8921,11 +8943,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8943,11 +8965,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8965,11 +8987,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8987,11 +9009,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -9009,11 +9031,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -9031,11 +9053,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -9053,11 +9075,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -9075,11 +9097,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -9097,11 +9119,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -9119,11 +9141,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -9141,11 +9163,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -9163,11 +9185,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -9185,11 +9207,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -9207,11 +9229,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -9229,11 +9251,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -9251,11 +9273,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -9273,11 +9295,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -9295,11 +9317,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -9317,11 +9339,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9339,11 +9361,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9361,11 +9383,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9383,11 +9405,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9405,11 +9427,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9427,11 +9449,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9449,11 +9471,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9471,11 +9493,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9493,11 +9515,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9515,11 +9537,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9537,11 +9559,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9559,11 +9581,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9581,11 +9603,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9603,11 +9625,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9625,11 +9647,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9647,11 +9669,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9669,11 +9691,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9691,11 +9713,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9713,11 +9735,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9735,11 +9757,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9757,11 +9779,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9779,11 +9801,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9801,11 +9823,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9823,11 +9845,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9845,11 +9867,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9867,11 +9889,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9889,11 +9911,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9911,11 +9933,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9933,11 +9955,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9955,11 +9977,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9977,11 +9999,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9999,11 +10021,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -10021,11 +10043,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -10043,11 +10065,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -10065,11 +10087,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -10087,11 +10109,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -10109,11 +10131,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -10131,11 +10153,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -10153,11 +10175,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -10175,11 +10197,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -10197,11 +10219,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -10219,11 +10241,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -10241,11 +10263,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -10263,11 +10285,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -10285,11 +10307,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -10307,11 +10329,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -10329,11 +10351,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10351,11 +10373,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10373,11 +10395,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10395,11 +10417,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10417,11 +10439,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10439,11 +10461,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10461,11 +10483,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10483,11 +10505,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10505,11 +10527,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10527,11 +10549,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10549,11 +10571,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10571,11 +10593,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10593,11 +10615,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10615,11 +10637,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10637,11 +10659,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10659,11 +10681,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10681,11 +10703,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10703,11 +10725,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10725,11 +10747,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10747,11 +10769,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10769,11 +10791,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10791,11 +10813,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10813,11 +10835,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10835,11 +10857,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10857,11 +10879,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10879,11 +10901,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10901,11 +10923,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10923,11 +10945,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10945,11 +10967,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10967,11 +10989,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10989,11 +11011,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -11011,11 +11033,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -11033,11 +11055,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -11055,11 +11077,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -11077,11 +11099,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -11099,11 +11121,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -11121,11 +11143,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -11143,11 +11165,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -11165,11 +11187,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -11187,11 +11209,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -11209,11 +11231,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -11231,11 +11253,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -11253,11 +11275,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6B8ED45B-7711-4B2E-98CB-BBB2443FC4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BC68F94-9DFD-4866-967A-BF4D003950C2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9DE351-BE3F-40CD-9561-4206EA26BAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3861,25 +3861,47 @@
       <c r="A65" s="8">
         <v>46308</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="B65" s="14">
+        <v>450</v>
+      </c>
+      <c r="C65" s="14">
+        <v>0</v>
+      </c>
+      <c r="D65" s="14">
+        <v>136</v>
+      </c>
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>201</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>787</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>653</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9DE351-BE3F-40CD-9561-4206EA26BAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3F9DE351-BE3F-40CD-9561-4206EA26BAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7A92F84-B287-4F06-8AE0-858C427F75FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3907,25 +3907,47 @@
       <c r="A66" s="8">
         <v>46309</v>
       </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+      <c r="B66" s="14">
+        <v>389</v>
+      </c>
+      <c r="C66" s="14">
+        <v>0</v>
+      </c>
+      <c r="D66" s="14">
+        <v>190</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>400</v>
+      </c>
+      <c r="I66" s="15">
+        <f t="shared" ref="I66" si="8">IF(SUM(B66:F66,H66)=0,"",SUM(B66:F66,H66))</f>
+        <v>979</v>
+      </c>
+      <c r="J66" s="15">
+        <f t="shared" ref="J66" si="9">IF(I66="","",1440-I66)</f>
+        <v>461</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
@@ -4011,11 +4033,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -4035,11 +4057,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -4059,11 +4081,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -4081,11 +4103,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -4103,11 +4125,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -4125,11 +4147,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -4147,11 +4169,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -4169,11 +4191,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -4191,11 +4213,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -4213,11 +4235,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -4235,11 +4257,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -4257,11 +4279,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -4279,11 +4301,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -4301,11 +4323,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -4323,11 +4345,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -4345,11 +4367,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -4367,11 +4389,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -4389,11 +4411,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -4411,11 +4433,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -4433,11 +4455,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -4455,11 +4477,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -4477,11 +4499,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4499,11 +4521,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4521,11 +4543,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4543,11 +4565,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4565,11 +4587,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4587,11 +4609,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4609,11 +4631,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4631,11 +4653,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4653,11 +4675,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4675,11 +4697,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4697,11 +4719,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4719,11 +4741,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4741,11 +4763,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4763,11 +4785,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4785,11 +4807,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4807,11 +4829,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4829,11 +4851,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4851,11 +4873,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4873,11 +4895,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4895,11 +4917,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4917,11 +4939,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4939,11 +4961,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4961,11 +4983,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4983,11 +5005,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -5005,11 +5027,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -5027,11 +5049,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -5049,11 +5071,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -5071,11 +5093,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -5093,11 +5115,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -5115,11 +5137,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -5137,11 +5159,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -5159,11 +5181,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -5181,11 +5203,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -5203,11 +5225,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -5225,11 +5247,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -5247,11 +5269,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -5269,11 +5291,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -5291,11 +5313,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -5313,11 +5335,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5335,11 +5357,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -5357,11 +5379,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -5379,11 +5401,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -5401,11 +5423,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5423,11 +5445,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5445,11 +5467,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5467,11 +5489,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5489,11 +5511,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5511,11 +5533,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5533,11 +5555,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5555,11 +5577,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5577,11 +5599,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5599,11 +5621,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5621,11 +5643,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5643,11 +5665,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5665,11 +5687,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5687,11 +5709,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5709,11 +5731,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5731,11 +5753,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5753,11 +5775,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5775,11 +5797,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5797,11 +5819,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5819,11 +5841,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5841,11 +5863,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5863,11 +5885,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5885,11 +5907,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5907,11 +5929,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5929,11 +5951,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5951,11 +5973,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5973,11 +5995,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5995,11 +6017,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -6017,11 +6039,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -6039,11 +6061,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -6061,11 +6083,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -6083,11 +6105,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -6105,11 +6127,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -6127,11 +6149,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -6149,11 +6171,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -6171,11 +6193,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -6193,11 +6215,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -6215,11 +6237,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -6237,11 +6259,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -6259,11 +6281,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -6281,11 +6303,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -6303,11 +6325,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -6325,11 +6347,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -6347,11 +6369,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -6369,11 +6391,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6391,11 +6413,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6413,11 +6435,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6435,11 +6457,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6457,11 +6479,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6479,11 +6501,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6501,11 +6523,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6523,11 +6545,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6545,11 +6567,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6567,11 +6589,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6589,11 +6611,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6611,11 +6633,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6633,11 +6655,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6655,11 +6677,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6677,11 +6699,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6699,11 +6721,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6721,11 +6743,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6743,11 +6765,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6765,11 +6787,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6787,11 +6809,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6809,11 +6831,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6831,11 +6853,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6853,11 +6875,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6875,11 +6897,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6897,11 +6919,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6919,11 +6941,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6941,11 +6963,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6963,11 +6985,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6985,11 +7007,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -7007,11 +7029,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -7029,11 +7051,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -7051,11 +7073,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -7073,11 +7095,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -7095,11 +7117,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -7117,11 +7139,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -7139,11 +7161,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -7161,11 +7183,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -7183,11 +7205,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -7205,11 +7227,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -7227,11 +7249,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -7249,11 +7271,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -7271,11 +7293,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -7293,11 +7315,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -7315,11 +7337,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -7337,11 +7359,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7359,11 +7381,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7381,11 +7403,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7403,11 +7425,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7425,11 +7447,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7447,11 +7469,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7469,11 +7491,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7491,11 +7513,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7513,11 +7535,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7535,11 +7557,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7557,11 +7579,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7579,11 +7601,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7601,11 +7623,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7623,11 +7645,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7645,11 +7667,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7667,11 +7689,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7689,11 +7711,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7711,11 +7733,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7733,11 +7755,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7755,11 +7777,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7777,11 +7799,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7799,11 +7821,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7821,11 +7843,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7843,11 +7865,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7865,11 +7887,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7887,11 +7909,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7909,11 +7931,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7931,11 +7953,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7953,11 +7975,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7975,11 +7997,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7997,11 +8019,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -8019,11 +8041,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -8041,11 +8063,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -8063,11 +8085,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -8085,11 +8107,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -8107,11 +8129,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -8129,11 +8151,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8151,11 +8173,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -8173,11 +8195,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -8195,11 +8217,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -8217,11 +8239,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -8239,11 +8261,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8261,11 +8283,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8283,11 +8305,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8305,11 +8327,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8327,11 +8349,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8349,11 +8371,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -8371,11 +8393,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8393,11 +8415,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8415,11 +8437,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8437,11 +8459,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8459,11 +8481,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8481,11 +8503,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8503,11 +8525,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8525,11 +8547,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8547,11 +8569,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8569,11 +8591,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8591,11 +8613,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8613,11 +8635,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8635,11 +8657,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8657,11 +8679,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8679,11 +8701,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8701,11 +8723,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8723,11 +8745,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8745,11 +8767,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8767,11 +8789,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8789,11 +8811,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8811,11 +8833,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8833,11 +8855,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8855,11 +8877,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8877,11 +8899,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8899,11 +8921,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8921,11 +8943,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8943,11 +8965,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8965,11 +8987,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8987,11 +9009,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -9009,11 +9031,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -9031,11 +9053,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -9053,11 +9075,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -9075,11 +9097,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -9097,11 +9119,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -9119,11 +9141,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -9141,11 +9163,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -9163,11 +9185,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -9185,11 +9207,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -9207,11 +9229,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -9229,11 +9251,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -9251,11 +9273,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -9273,11 +9295,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -9295,11 +9317,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -9317,11 +9339,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -9339,11 +9361,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -9361,11 +9383,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9383,11 +9405,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9405,11 +9427,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9427,11 +9449,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9449,11 +9471,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9471,11 +9493,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9493,11 +9515,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9515,11 +9537,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9537,11 +9559,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9559,11 +9581,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9581,11 +9603,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9603,11 +9625,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9625,11 +9647,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9647,11 +9669,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9669,11 +9691,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9691,11 +9713,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9713,11 +9735,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9735,11 +9757,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9757,11 +9779,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9779,11 +9801,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9801,11 +9823,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9823,11 +9845,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9845,11 +9867,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9867,11 +9889,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9889,11 +9911,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9911,11 +9933,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9933,11 +9955,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9955,11 +9977,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9977,11 +9999,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9999,11 +10021,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -10021,11 +10043,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -10043,11 +10065,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -10065,11 +10087,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -10087,11 +10109,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -10109,11 +10131,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -10131,11 +10153,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -10153,11 +10175,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -10175,11 +10197,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -10197,11 +10219,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -10219,11 +10241,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -10241,11 +10263,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -10263,11 +10285,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -10285,11 +10307,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -10307,11 +10329,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -10329,11 +10351,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -10351,11 +10373,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -10373,11 +10395,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10395,11 +10417,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10417,11 +10439,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10439,11 +10461,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10461,11 +10483,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10483,11 +10505,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10505,11 +10527,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10527,11 +10549,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10549,11 +10571,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10571,11 +10593,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10593,11 +10615,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10615,11 +10637,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10637,11 +10659,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10659,11 +10681,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10681,11 +10703,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10703,11 +10725,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10725,11 +10747,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10747,11 +10769,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10769,11 +10791,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10791,11 +10813,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10813,11 +10835,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10835,11 +10857,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10857,11 +10879,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10879,11 +10901,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10901,11 +10923,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10923,11 +10945,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10945,11 +10967,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10967,11 +10989,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10989,11 +11011,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -11011,11 +11033,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -11033,11 +11055,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -11055,11 +11077,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -11077,11 +11099,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -11099,11 +11121,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -11121,11 +11143,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -11143,11 +11165,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -11165,11 +11187,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -11187,11 +11209,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -11209,11 +11231,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -11231,11 +11253,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -11253,11 +11275,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -11275,11 +11297,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -11297,11 +11319,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3F9DE351-BE3F-40CD-9561-4206EA26BAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7A92F84-B287-4F06-8AE0-858C427F75FE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3953,25 +3953,47 @@
       <c r="A67" s="8">
         <v>46310</v>
       </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+      <c r="B67" s="14">
+        <v>720</v>
+      </c>
+      <c r="C67" s="14">
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <v>240</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>210</v>
+      </c>
+      <c r="I67" s="15">
+        <f t="shared" ref="I67" si="10">IF(SUM(B67:F67,H67)=0,"",SUM(B67:F67,H67))</f>
+        <v>1170</v>
+      </c>
+      <c r="J67" s="15">
+        <f t="shared" ref="J67" si="11">IF(I67="","",1440-I67)</f>
+        <v>270</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
@@ -4033,11 +4055,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -4057,11 +4079,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -4081,11 +4103,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -4103,11 +4125,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -4125,11 +4147,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -4147,11 +4169,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -4169,11 +4191,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -4191,11 +4213,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -4213,11 +4235,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -4235,11 +4257,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -4257,11 +4279,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -4279,11 +4301,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -4301,11 +4323,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -4323,11 +4345,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -4345,11 +4367,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -4367,11 +4389,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -4389,11 +4411,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -4411,11 +4433,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -4433,11 +4455,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -4455,11 +4477,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -4477,11 +4499,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -4499,11 +4521,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4521,11 +4543,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4543,11 +4565,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4565,11 +4587,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4587,11 +4609,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4609,11 +4631,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4631,11 +4653,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4653,11 +4675,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4675,11 +4697,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4697,11 +4719,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4719,11 +4741,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4741,11 +4763,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4763,11 +4785,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4785,11 +4807,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4807,11 +4829,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4829,11 +4851,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4851,11 +4873,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4873,11 +4895,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4895,11 +4917,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4917,11 +4939,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4939,11 +4961,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4961,11 +4983,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4983,11 +5005,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -5005,11 +5027,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -5027,11 +5049,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -5049,11 +5071,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -5071,11 +5093,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -5093,11 +5115,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -5115,11 +5137,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -5137,11 +5159,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -5159,11 +5181,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -5181,11 +5203,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -5203,11 +5225,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -5225,11 +5247,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -5247,11 +5269,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -5269,11 +5291,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -5291,11 +5313,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -5313,11 +5335,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -5335,11 +5357,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5357,11 +5379,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -5379,11 +5401,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -5401,11 +5423,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -5423,11 +5445,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5445,11 +5467,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="14">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="15">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5467,11 +5489,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5489,11 +5511,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5511,11 +5533,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5533,11 +5555,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5555,11 +5577,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5577,11 +5599,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5599,11 +5621,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5621,11 +5643,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5643,11 +5665,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5665,11 +5687,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5687,11 +5709,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5709,11 +5731,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5731,11 +5753,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5753,11 +5775,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5775,11 +5797,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5797,11 +5819,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5819,11 +5841,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5841,11 +5863,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5863,11 +5885,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5885,11 +5907,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5907,11 +5929,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5929,11 +5951,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5951,11 +5973,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5973,11 +5995,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5995,11 +6017,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -6017,11 +6039,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -6039,11 +6061,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -6061,11 +6083,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -6083,11 +6105,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -6105,11 +6127,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -6127,11 +6149,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -6149,11 +6171,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -6171,11 +6193,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -6193,11 +6215,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -6215,11 +6237,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -6237,11 +6259,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -6259,11 +6281,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -6281,11 +6303,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -6303,11 +6325,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -6325,11 +6347,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -6347,11 +6369,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -6369,11 +6391,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -6391,11 +6413,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6413,11 +6435,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6435,11 +6457,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6457,11 +6479,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6479,11 +6501,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6501,11 +6523,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6523,11 +6545,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6545,11 +6567,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6567,11 +6589,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6589,11 +6611,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6611,11 +6633,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6633,11 +6655,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6655,11 +6677,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6677,11 +6699,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6699,11 +6721,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6721,11 +6743,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6743,11 +6765,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6765,11 +6787,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6787,11 +6809,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6809,11 +6831,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6831,11 +6853,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6853,11 +6875,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="16">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="17">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6875,11 +6897,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6897,11 +6919,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6919,11 +6941,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6941,11 +6963,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6963,11 +6985,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6985,11 +7007,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -7007,11 +7029,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -7029,11 +7051,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -7051,11 +7073,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -7073,11 +7095,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -7095,11 +7117,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -7117,11 +7139,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -7139,11 +7161,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -7161,11 +7183,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -7183,11 +7205,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -7205,11 +7227,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -7227,11 +7249,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -7249,11 +7271,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -7271,11 +7293,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -7293,11 +7315,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -7315,11 +7337,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -7337,11 +7359,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -7359,11 +7381,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7381,11 +7403,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7403,11 +7425,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7425,11 +7447,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7447,11 +7469,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7469,11 +7491,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7491,11 +7513,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7513,11 +7535,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7535,11 +7557,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7557,11 +7579,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7579,11 +7601,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7601,11 +7623,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7623,11 +7645,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7645,11 +7667,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7667,11 +7689,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7689,11 +7711,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7711,11 +7733,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7733,11 +7755,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7755,11 +7777,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7777,11 +7799,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7799,11 +7821,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7821,11 +7843,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7843,11 +7865,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7865,11 +7887,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7887,11 +7909,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7909,11 +7931,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7931,11 +7953,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7953,11 +7975,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7975,11 +7997,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7997,11 +8019,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -8019,11 +8041,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -8041,11 +8063,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -8063,11 +8085,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -8085,11 +8107,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -8107,11 +8129,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -8129,11 +8151,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -8151,11 +8173,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8173,11 +8195,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -8195,11 +8217,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -8217,11 +8239,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -8239,11 +8261,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -8261,11 +8283,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="18">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="19">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8283,11 +8305,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8305,11 +8327,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8327,11 +8349,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8349,11 +8371,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8371,11 +8393,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -8393,11 +8415,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8415,11 +8437,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8437,11 +8459,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8459,11 +8481,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8481,11 +8503,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8503,11 +8525,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8525,11 +8547,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8547,11 +8569,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8569,11 +8591,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8591,11 +8613,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8613,11 +8635,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8635,11 +8657,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8657,11 +8679,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8679,11 +8701,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8701,11 +8723,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8723,11 +8745,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8745,11 +8767,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8767,11 +8789,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8789,11 +8811,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8811,11 +8833,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8833,11 +8855,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8855,11 +8877,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8877,11 +8899,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8899,11 +8921,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8921,11 +8943,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8943,11 +8965,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8965,11 +8987,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8987,11 +9009,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -9009,11 +9031,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -9031,11 +9053,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -9053,11 +9075,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -9075,11 +9097,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -9097,11 +9119,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -9119,11 +9141,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -9141,11 +9163,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -9163,11 +9185,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -9185,11 +9207,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -9207,11 +9229,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -9229,11 +9251,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -9251,11 +9273,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -9273,11 +9295,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -9295,11 +9317,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -9317,11 +9339,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -9339,11 +9361,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -9361,11 +9383,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -9383,11 +9405,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9405,11 +9427,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9427,11 +9449,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9449,11 +9471,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9471,11 +9493,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9493,11 +9515,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9515,11 +9537,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9537,11 +9559,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9559,11 +9581,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9581,11 +9603,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9603,11 +9625,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9625,11 +9647,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9647,11 +9669,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9669,11 +9691,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="20">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="21">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9691,11 +9713,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9713,11 +9735,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9735,11 +9757,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9757,11 +9779,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9779,11 +9801,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9801,11 +9823,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9823,11 +9845,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9845,11 +9867,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9867,11 +9889,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9889,11 +9911,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9911,11 +9933,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9933,11 +9955,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9955,11 +9977,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9977,11 +9999,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9999,11 +10021,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -10021,11 +10043,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -10043,11 +10065,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -10065,11 +10087,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -10087,11 +10109,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -10109,11 +10131,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -10131,11 +10153,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -10153,11 +10175,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -10175,11 +10197,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -10197,11 +10219,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -10219,11 +10241,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -10241,11 +10263,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -10263,11 +10285,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -10285,11 +10307,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -10307,11 +10329,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -10329,11 +10351,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -10351,11 +10373,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -10373,11 +10395,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -10395,11 +10417,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10417,11 +10439,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10439,11 +10461,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10461,11 +10483,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10483,11 +10505,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10505,11 +10527,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10527,11 +10549,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10549,11 +10571,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10571,11 +10593,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10593,11 +10615,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10615,11 +10637,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10637,11 +10659,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10659,11 +10681,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10681,11 +10703,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10703,11 +10725,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10725,11 +10747,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10747,11 +10769,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10769,11 +10791,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10791,11 +10813,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10813,11 +10835,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10835,11 +10857,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10857,11 +10879,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10879,11 +10901,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10901,11 +10923,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10923,11 +10945,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10945,11 +10967,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10967,11 +10989,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10989,11 +11011,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -11011,11 +11033,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -11033,11 +11055,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -11055,11 +11077,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -11077,11 +11099,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="22">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="23">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -11099,11 +11121,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -11121,11 +11143,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -11143,11 +11165,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -11165,11 +11187,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -11187,11 +11209,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -11209,11 +11231,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -11231,11 +11253,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -11253,11 +11275,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -11275,11 +11297,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -11297,11 +11319,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -11319,11 +11341,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31BB252-8B31-4EEE-A92B-FF7F2E3BA1F7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -354,6 +354,9 @@
   <si>
     <t>Was Studying for MTT</t>
   </si>
+  <si>
+    <t>Was at a Family gathering</t>
+  </si>
 </sst>
 </file>
 
@@ -539,7 +542,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3770,7 +3785,7 @@
         <v>46306</v>
       </c>
       <c r="B63" s="14">
-        <v>780</v>
+        <v>620</v>
       </c>
       <c r="C63" s="14">
         <v>0</v>
@@ -3792,11 +3807,11 @@
       </c>
       <c r="I63" s="15">
         <f t="shared" ref="I63" si="4">IF(SUM(B63:F63,H63)=0,"",SUM(B63:F63,H63))</f>
-        <v>1204</v>
+        <v>1044</v>
       </c>
       <c r="J63" s="15">
         <f t="shared" ref="J63" si="5">IF(I63="","",1440-I63)</f>
-        <v>236</v>
+        <v>396</v>
       </c>
       <c r="K63" s="16" t="s">
         <v>61</v>
@@ -3999,73 +4014,133 @@
       <c r="A68" s="8">
         <v>46311</v>
       </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="B68" s="14">
+        <v>450</v>
+      </c>
+      <c r="C68" s="14">
+        <v>0</v>
+      </c>
+      <c r="D68" s="14">
+        <v>240</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
       <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>46312</v>
       </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
+      <c r="B69" s="14">
+        <v>480</v>
+      </c>
+      <c r="C69" s="14">
+        <v>0</v>
+      </c>
+      <c r="D69" s="14">
+        <v>190</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
       <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>770</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>46313</v>
       </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
+      <c r="B70" s="14">
+        <v>698</v>
+      </c>
+      <c r="C70" s="14">
+        <v>0</v>
+      </c>
+      <c r="D70" s="14">
+        <v>0</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
       <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>698</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>742</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
@@ -11363,12 +11438,12 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J22 J24:J401">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31BB252-8B31-4EEE-A92B-FF7F2E3BA1F7}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BADC91B4-9C7E-454D-9F77-838496E6DBD7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -542,19 +542,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4032,14 +4020,16 @@
       <c r="G68" s="14">
         <v>0</v>
       </c>
-      <c r="H68" s="14"/>
+      <c r="H68" s="14">
+        <v>450</v>
+      </c>
       <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>1140</v>
       </c>
       <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="K68" s="16" t="s">
         <v>58</v>
@@ -4076,14 +4066,16 @@
       <c r="G69" s="14">
         <v>0</v>
       </c>
-      <c r="H69" s="14"/>
+      <c r="H69" s="14">
+        <v>542</v>
+      </c>
       <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v>670</v>
+        <v>1212</v>
       </c>
       <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v>770</v>
+        <v>228</v>
       </c>
       <c r="K69" s="16" t="s">
         <v>57</v>
@@ -4120,14 +4112,16 @@
       <c r="G70" s="14">
         <v>0</v>
       </c>
-      <c r="H70" s="14"/>
+      <c r="H70" s="14">
+        <v>600</v>
+      </c>
       <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v>698</v>
+        <v>1298</v>
       </c>
       <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
-        <v>742</v>
+        <v>142</v>
       </c>
       <c r="K70" s="16" t="s">
         <v>57</v>
@@ -4146,25 +4140,47 @@
       <c r="A71" s="8">
         <v>46314</v>
       </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="B71" s="14">
+        <v>420</v>
+      </c>
+      <c r="C71" s="14">
+        <v>120</v>
+      </c>
+      <c r="D71" s="14">
+        <v>60</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>150</v>
+      </c>
+      <c r="G71" s="14">
+        <v>3</v>
+      </c>
+      <c r="H71" s="14">
+        <v>400</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
@@ -11438,12 +11454,12 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J22 J24:J401">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BADC91B4-9C7E-454D-9F77-838496E6DBD7}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{066A7D8D-4FD4-457D-8388-8B30A910356A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>Was at a Family gathering</t>
+  </si>
+  <si>
+    <t>Was Dusshera</t>
   </si>
 </sst>
 </file>
@@ -4186,25 +4189,47 @@
       <c r="A72" s="8">
         <v>46315</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="B72" s="14">
+        <v>420</v>
+      </c>
+      <c r="C72" s="14">
+        <v>0</v>
+      </c>
+      <c r="D72" s="14">
+        <v>0</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>600</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{7720CF86-B81C-4DE7-8239-C1F3A61B6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{066A7D8D-4FD4-457D-8388-8B30A910356A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D1BCF8-0131-4EE2-9FF2-91038CB7E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>Was Dusshera</t>
+  </si>
+  <si>
+    <t>Was with Friends</t>
   </si>
 </sst>
 </file>
@@ -4232,48 +4235,96 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B73" s="14">
+        <v>480</v>
+      </c>
+      <c r="C73" s="14">
+        <v>120</v>
+      </c>
+      <c r="D73" s="14">
+        <v>60</v>
+      </c>
+      <c r="E73" s="14">
+        <v>15</v>
+      </c>
+      <c r="F73" s="14">
+        <v>100</v>
+      </c>
+      <c r="G73" s="14">
+        <v>2</v>
+      </c>
+      <c r="H73" s="14">
+        <v>450</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1225</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>215</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B74" s="14">
+        <v>380</v>
+      </c>
+      <c r="C74" s="14">
+        <v>60</v>
+      </c>
+      <c r="D74" s="14">
+        <v>0</v>
+      </c>
+      <c r="E74" s="14">
+        <v>30</v>
+      </c>
+      <c r="F74" s="14">
+        <v>300</v>
+      </c>
+      <c r="G74" s="14">
+        <v>6</v>
+      </c>
+      <c r="H74" s="14">
+        <v>520</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\cap-760\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D1BCF8-0131-4EE2-9FF2-91038CB7E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{21D1BCF8-0131-4EE2-9FF2-91038CB7E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F7CE0D3-81F6-40E6-AB3C-B68E232F69B6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4327,29 +4327,55 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="14">
+        <v>390</v>
+      </c>
+      <c r="C75" s="14">
+        <v>120</v>
+      </c>
+      <c r="D75" s="14">
+        <v>60</v>
+      </c>
+      <c r="E75" s="14">
+        <v>45</v>
+      </c>
+      <c r="F75" s="14">
+        <v>300</v>
+      </c>
+      <c r="G75" s="14">
+        <v>6</v>
+      </c>
+      <c r="H75" s="14">
+        <v>350</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>1265</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>175</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
+      <c r="A76" s="8">
+        <v>46319</v>
+      </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -4371,7 +4397,9 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
+      <c r="A77" s="8">
+        <v>46320</v>
+      </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -4393,7 +4421,9 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
+      <c r="A78" s="8">
+        <v>46321</v>
+      </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -4415,7 +4445,9 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
+      <c r="A79" s="8">
+        <v>46322</v>
+      </c>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{21D1BCF8-0131-4EE2-9FF2-91038CB7E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F7CE0D3-81F6-40E6-AB3C-B68E232F69B6}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{21D1BCF8-0131-4EE2-9FF2-91038CB7E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DD8BB8A-E54B-4044-B581-90C80B8BAF8D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4376,49 +4376,93 @@
       <c r="A76" s="8">
         <v>46319</v>
       </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="B76" s="14">
+        <v>480</v>
+      </c>
+      <c r="C76" s="14">
+        <v>120</v>
+      </c>
+      <c r="D76" s="14">
+        <v>49</v>
+      </c>
+      <c r="E76" s="14">
+        <v>30</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>400</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1079</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>361</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>46320</v>
       </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="B77" s="14">
+        <v>500</v>
+      </c>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="14">
+        <v>0</v>
+      </c>
+      <c r="E77" s="14">
+        <v>0</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>654</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>1154</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>286</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="8">

--- a/12625479.xlsx
+++ b/12625479.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047698fab5a02d10/Desktop/cap-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{21D1BCF8-0131-4EE2-9FF2-91038CB7E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DD8BB8A-E54B-4044-B581-90C80B8BAF8D}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{21D1BCF8-0131-4EE2-9FF2-91038CB7E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C2F29F6-5E4B-423F-9B98-45BB7B0640CD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Was with Friends</t>
+  </si>
+  <si>
+    <t>Enjoying Holiday</t>
   </si>
 </sst>
 </file>
@@ -4468,25 +4471,47 @@
       <c r="A78" s="8">
         <v>46321</v>
       </c>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="B78" s="14">
+        <v>480</v>
+      </c>
+      <c r="C78" s="14">
+        <v>120</v>
+      </c>
+      <c r="D78" s="14">
+        <v>60</v>
+      </c>
+      <c r="E78" s="14">
+        <v>45</v>
+      </c>
+      <c r="F78" s="14">
+        <v>0</v>
+      </c>
+      <c r="G78" s="14">
+        <v>0</v>
+      </c>
+      <c r="H78" s="14">
+        <v>455</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
